--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -11419,7 +11419,7 @@
       </c>
       <c r="C163" s="10"/>
       <c r="D163" s="9">
-        <v>46231.66783722222</v>
+        <v>46279.14898133102</v>
       </c>
       <c r="E163" s="10" t="s">
         <v>333</v>
@@ -11463,8 +11463,8 @@
       <c r="R163" s="9">
         <v>46286</v>
       </c>
-      <c r="S163" s="7" t="s">
-        <v>32</v>
+      <c r="S163" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="T163" s="10">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -6972,7 +6972,7 @@
       </c>
       <c r="C80" s="6"/>
       <c r="D80" s="5">
-        <v>46274.12650756944</v>
+        <v>46280.16892150463</v>
       </c>
       <c r="E80" s="6" t="s">
         <v>213</v>
@@ -7035,7 +7035,7 @@
       </c>
       <c r="C81" s="10"/>
       <c r="D81" s="9">
-        <v>46260.6623522338</v>
+        <v>46280.16892443287</v>
       </c>
       <c r="E81" s="10" t="s">
         <v>134</v>
@@ -7088,7 +7088,7 @@
       </c>
       <c r="C82" s="6"/>
       <c r="D82" s="5">
-        <v>46260.662350914354</v>
+        <v>46280.16892314814</v>
       </c>
       <c r="E82" s="6" t="s">
         <v>134</v>
@@ -7141,7 +7141,7 @@
       </c>
       <c r="C83" s="10"/>
       <c r="D83" s="9">
-        <v>46260.662350370374</v>
+        <v>46280.16892023148</v>
       </c>
       <c r="E83" s="10" t="s">
         <v>134</v>
@@ -7194,7 +7194,7 @@
       </c>
       <c r="C84" s="6"/>
       <c r="D84" s="5">
-        <v>46238.48778649306</v>
+        <v>46280.1689183912</v>
       </c>
       <c r="E84" s="6" t="s">
         <v>134</v>
@@ -7247,7 +7247,7 @@
       </c>
       <c r="C85" s="10"/>
       <c r="D85" s="9">
-        <v>46238.48778996528</v>
+        <v>46280.16886712963</v>
       </c>
       <c r="E85" s="10" t="s">
         <v>134</v>
@@ -7300,7 +7300,7 @@
       </c>
       <c r="C86" s="6"/>
       <c r="D86" s="5">
-        <v>46238.48778768518</v>
+        <v>46280.16886854167</v>
       </c>
       <c r="E86" s="6" t="s">
         <v>134</v>
@@ -7353,7 +7353,7 @@
       </c>
       <c r="C87" s="10"/>
       <c r="D87" s="9">
-        <v>46238.48778834491</v>
+        <v>46280.16886958333</v>
       </c>
       <c r="E87" s="10" t="s">
         <v>134</v>
@@ -7406,7 +7406,7 @@
       </c>
       <c r="C88" s="6"/>
       <c r="D88" s="5">
-        <v>46238.48778460648</v>
+        <v>46280.16887061343</v>
       </c>
       <c r="E88" s="6" t="s">
         <v>134</v>
@@ -7459,7 +7459,7 @@
       </c>
       <c r="C89" s="10"/>
       <c r="D89" s="9">
-        <v>46238.48779039352</v>
+        <v>46280.16887173611</v>
       </c>
       <c r="E89" s="10" t="s">
         <v>134</v>
@@ -7512,7 +7512,7 @@
       </c>
       <c r="C90" s="6"/>
       <c r="D90" s="5">
-        <v>46238.4877950463</v>
+        <v>46280.168872800925</v>
       </c>
       <c r="E90" s="6" t="s">
         <v>134</v>
@@ -7565,7 +7565,7 @@
       </c>
       <c r="C91" s="10"/>
       <c r="D91" s="9">
-        <v>46238.48779283564</v>
+        <v>46280.16887384259</v>
       </c>
       <c r="E91" s="10" t="s">
         <v>134</v>
@@ -7618,7 +7618,7 @@
       </c>
       <c r="C92" s="6"/>
       <c r="D92" s="5">
-        <v>46238.487791493055</v>
+        <v>46280.16887483797</v>
       </c>
       <c r="E92" s="6" t="s">
         <v>134</v>
@@ -7671,7 +7671,7 @@
       </c>
       <c r="C93" s="10"/>
       <c r="D93" s="9">
-        <v>46238.48778605324</v>
+        <v>46280.16887583333</v>
       </c>
       <c r="E93" s="10" t="s">
         <v>134</v>
@@ -7724,7 +7724,7 @@
       </c>
       <c r="C94" s="6"/>
       <c r="D94" s="5">
-        <v>46238.48778420139</v>
+        <v>46280.16887688657</v>
       </c>
       <c r="E94" s="6" t="s">
         <v>134</v>
@@ -7777,7 +7777,7 @@
       </c>
       <c r="C95" s="10"/>
       <c r="D95" s="9">
-        <v>46238.48779195602</v>
+        <v>46280.168877986114</v>
       </c>
       <c r="E95" s="10" t="s">
         <v>134</v>
@@ -7830,7 +7830,7 @@
       </c>
       <c r="C96" s="6"/>
       <c r="D96" s="5">
-        <v>46238.487793657405</v>
+        <v>46280.16887907407</v>
       </c>
       <c r="E96" s="6" t="s">
         <v>138</v>
@@ -7883,7 +7883,7 @@
       </c>
       <c r="C97" s="10"/>
       <c r="D97" s="9">
-        <v>46238.48779326389</v>
+        <v>46280.16888006944</v>
       </c>
       <c r="E97" s="10" t="s">
         <v>138</v>
@@ -7936,7 +7936,7 @@
       </c>
       <c r="C98" s="6"/>
       <c r="D98" s="5">
-        <v>46238.48778962963</v>
+        <v>46280.16888210648</v>
       </c>
       <c r="E98" s="6" t="s">
         <v>138</v>
@@ -7989,7 +7989,7 @@
       </c>
       <c r="C99" s="10"/>
       <c r="D99" s="9">
-        <v>46238.48778335648</v>
+        <v>46280.16888420139</v>
       </c>
       <c r="E99" s="10" t="s">
         <v>138</v>
@@ -8042,7 +8042,7 @@
       </c>
       <c r="C100" s="6"/>
       <c r="D100" s="5">
-        <v>46238.48778688657</v>
+        <v>46280.16888518519</v>
       </c>
       <c r="E100" s="6" t="s">
         <v>138</v>
@@ -8095,7 +8095,7 @@
       </c>
       <c r="C101" s="10"/>
       <c r="D101" s="9">
-        <v>46238.487783749995</v>
+        <v>46280.16888627315</v>
       </c>
       <c r="E101" s="10" t="s">
         <v>138</v>
@@ -8148,7 +8148,7 @@
       </c>
       <c r="C102" s="6"/>
       <c r="D102" s="5">
-        <v>46238.48779547453</v>
+        <v>46280.16888752315</v>
       </c>
       <c r="E102" s="6" t="s">
         <v>138</v>
@@ -8201,7 +8201,7 @@
       </c>
       <c r="C103" s="10"/>
       <c r="D103" s="9">
-        <v>46238.48778292824</v>
+        <v>46280.168888541666</v>
       </c>
       <c r="E103" s="10" t="s">
         <v>138</v>
@@ -8254,7 +8254,7 @@
       </c>
       <c r="C104" s="6"/>
       <c r="D104" s="5">
-        <v>46238.487793900465</v>
+        <v>46280.168883148144</v>
       </c>
       <c r="E104" s="6" t="s">
         <v>138</v>
@@ -8307,7 +8307,7 @@
       </c>
       <c r="C105" s="10"/>
       <c r="D105" s="9">
-        <v>46238.48778729167</v>
+        <v>46280.16888109954</v>
       </c>
       <c r="E105" s="10" t="s">
         <v>138</v>
@@ -12807,7 +12807,7 @@
       </c>
       <c r="C189" s="10"/>
       <c r="D189" s="9">
-        <v>46231.66796983796</v>
+        <v>46280.14267475695</v>
       </c>
       <c r="E189" s="10" t="s">
         <v>367</v>
@@ -12851,8 +12851,8 @@
       <c r="R189" s="9">
         <v>46287</v>
       </c>
-      <c r="S189" s="7" t="s">
-        <v>32</v>
+      <c r="S189" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="T189" s="10">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -8360,7 +8360,7 @@
       </c>
       <c r="C106" s="6"/>
       <c r="D106" s="5">
-        <v>46275.13813133102</v>
+        <v>46281.16867694445</v>
       </c>
       <c r="E106" s="6" t="s">
         <v>250</v>
@@ -8423,7 +8423,7 @@
       </c>
       <c r="C107" s="10"/>
       <c r="D107" s="9">
-        <v>46238.48777921296</v>
+        <v>46281.168681875</v>
       </c>
       <c r="E107" s="10" t="s">
         <v>134</v>
@@ -8476,7 +8476,7 @@
       </c>
       <c r="C108" s="6"/>
       <c r="D108" s="5">
-        <v>46238.487780752315</v>
+        <v>46281.16868296296</v>
       </c>
       <c r="E108" s="6" t="s">
         <v>134</v>
@@ -8529,7 +8529,7 @@
       </c>
       <c r="C109" s="10"/>
       <c r="D109" s="9">
-        <v>46238.4877812037</v>
+        <v>46281.16868633102</v>
       </c>
       <c r="E109" s="10" t="s">
         <v>134</v>
@@ -8582,7 +8582,7 @@
       </c>
       <c r="C110" s="6"/>
       <c r="D110" s="5">
-        <v>46231.66672795139</v>
+        <v>46281.16867881945</v>
       </c>
       <c r="E110" s="6" t="s">
         <v>134</v>
@@ -8635,7 +8635,7 @@
       </c>
       <c r="C111" s="10"/>
       <c r="D111" s="9">
-        <v>46238.487785000005</v>
+        <v>46281.16863071759</v>
       </c>
       <c r="E111" s="10" t="s">
         <v>134</v>
@@ -8688,7 +8688,7 @@
       </c>
       <c r="C112" s="6"/>
       <c r="D112" s="5">
-        <v>46231.66672108797</v>
+        <v>46281.168632754634</v>
       </c>
       <c r="E112" s="6" t="s">
         <v>134</v>
@@ -8741,7 +8741,7 @@
       </c>
       <c r="C113" s="10"/>
       <c r="D113" s="9">
-        <v>46238.48779480324</v>
+        <v>46281.16863375</v>
       </c>
       <c r="E113" s="10" t="s">
         <v>134</v>
@@ -8794,7 +8794,7 @@
       </c>
       <c r="C114" s="6"/>
       <c r="D114" s="5">
-        <v>46231.66671467593</v>
+        <v>46281.16863486111</v>
       </c>
       <c r="E114" s="6" t="s">
         <v>134</v>
@@ -8847,7 +8847,7 @@
       </c>
       <c r="C115" s="10"/>
       <c r="D115" s="9">
-        <v>46231.66671130787</v>
+        <v>46281.16863601852</v>
       </c>
       <c r="E115" s="10" t="s">
         <v>134</v>
@@ -8900,7 +8900,7 @@
       </c>
       <c r="C116" s="6"/>
       <c r="D116" s="5">
-        <v>46238.487792395834</v>
+        <v>46281.16863699074</v>
       </c>
       <c r="E116" s="6" t="s">
         <v>134</v>
@@ -8953,7 +8953,7 @@
       </c>
       <c r="C117" s="10"/>
       <c r="D117" s="9">
-        <v>46238.487790949075</v>
+        <v>46281.168637986106</v>
       </c>
       <c r="E117" s="10" t="s">
         <v>134</v>
@@ -9006,7 +9006,7 @@
       </c>
       <c r="C118" s="6"/>
       <c r="D118" s="5">
-        <v>46231.66670135417</v>
+        <v>46281.168639131945</v>
       </c>
       <c r="E118" s="6" t="s">
         <v>134</v>
@@ -9059,7 +9059,7 @@
       </c>
       <c r="C119" s="10"/>
       <c r="D119" s="9">
-        <v>46238.48779597222</v>
+        <v>46281.16864011574</v>
       </c>
       <c r="E119" s="10" t="s">
         <v>134</v>
@@ -9112,7 +9112,7 @@
       </c>
       <c r="C120" s="6"/>
       <c r="D120" s="5">
-        <v>46231.66669519676</v>
+        <v>46281.16864106481</v>
       </c>
       <c r="E120" s="6" t="s">
         <v>134</v>
@@ -9165,7 +9165,7 @@
       </c>
       <c r="C121" s="10"/>
       <c r="D121" s="9">
-        <v>46231.66669142361</v>
+        <v>46281.16864203704</v>
       </c>
       <c r="E121" s="10" t="s">
         <v>134</v>
@@ -9218,7 +9218,7 @@
       </c>
       <c r="C122" s="6"/>
       <c r="D122" s="5">
-        <v>46231.66668751158</v>
+        <v>46281.16864309028</v>
       </c>
       <c r="E122" s="6" t="s">
         <v>138</v>
@@ -9271,7 +9271,7 @@
       </c>
       <c r="C123" s="10"/>
       <c r="D123" s="9">
-        <v>46231.66668429398</v>
+        <v>46281.168644108795</v>
       </c>
       <c r="E123" s="10" t="s">
         <v>138</v>
@@ -9324,7 +9324,7 @@
       </c>
       <c r="C124" s="6"/>
       <c r="D124" s="5">
-        <v>46231.66667890047</v>
+        <v>46281.16864525463</v>
       </c>
       <c r="E124" s="6" t="s">
         <v>138</v>
@@ -9377,7 +9377,7 @@
       </c>
       <c r="C125" s="10"/>
       <c r="D125" s="9">
-        <v>46231.66666850694</v>
+        <v>46281.16864621528</v>
       </c>
       <c r="E125" s="10" t="s">
         <v>138</v>
@@ -9430,7 +9430,7 @@
       </c>
       <c r="C126" s="6"/>
       <c r="D126" s="5">
-        <v>46231.66667090278</v>
+        <v>46281.16864721065</v>
       </c>
       <c r="E126" s="6" t="s">
         <v>138</v>
@@ -9483,7 +9483,7 @@
       </c>
       <c r="C127" s="10"/>
       <c r="D127" s="9">
-        <v>46240.823163877314</v>
+        <v>46281.16864822917</v>
       </c>
       <c r="E127" s="10" t="s">
         <v>138</v>
@@ -9536,7 +9536,7 @@
       </c>
       <c r="C128" s="6"/>
       <c r="D128" s="5">
-        <v>46240.82316032407</v>
+        <v>46281.168649259256</v>
       </c>
       <c r="E128" s="6" t="s">
         <v>138</v>
@@ -9589,7 +9589,7 @@
       </c>
       <c r="C129" s="10"/>
       <c r="D129" s="9">
-        <v>46240.8231571412</v>
+        <v>46281.16865019676</v>
       </c>
       <c r="E129" s="10" t="s">
         <v>138</v>
@@ -9642,7 +9642,7 @@
       </c>
       <c r="C130" s="6"/>
       <c r="D130" s="5">
-        <v>46240.823153680554</v>
+        <v>46281.168651527776</v>
       </c>
       <c r="E130" s="6" t="s">
         <v>138</v>
@@ -9695,7 +9695,7 @@
       </c>
       <c r="C131" s="10"/>
       <c r="D131" s="9">
-        <v>46240.82315002315</v>
+        <v>46281.16865258102</v>
       </c>
       <c r="E131" s="10" t="s">
         <v>138</v>
@@ -14195,7 +14195,7 @@
       </c>
       <c r="C215" s="10"/>
       <c r="D215" s="9">
-        <v>46231.66840002315</v>
+        <v>46281.1451984375</v>
       </c>
       <c r="E215" s="10" t="s">
         <v>398</v>
@@ -14239,8 +14239,8 @@
       <c r="R215" s="9">
         <v>46288</v>
       </c>
-      <c r="S215" s="7" t="s">
-        <v>32</v>
+      <c r="S215" s="12" t="s">
+        <v>302</v>
       </c>
       <c r="T215" s="10">
         <v>0</v>

--- a/data/50001583 - xemortiz stock.xlsx
+++ b/data/50001583 - xemortiz stock.xlsx
@@ -957,106 +957,106 @@
     <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
   </si>
   <si>
+    <t>1216950807852788</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950807852806</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950957312170</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
+    <t>1216950957319489</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 </t>
+  </si>
+  <si>
+    <t>1216916670897023</t>
+  </si>
+  <si>
+    <t>1216916670897024</t>
+  </si>
+  <si>
+    <t>1216916670897025</t>
+  </si>
+  <si>
+    <t>1216916670897026</t>
+  </si>
+  <si>
+    <t>1216916670897027</t>
+  </si>
+  <si>
+    <t>1216916670897028</t>
+  </si>
+  <si>
+    <t>1216916670897029</t>
+  </si>
+  <si>
+    <t>1216916670897030</t>
+  </si>
+  <si>
+    <t>1216916670897031</t>
+  </si>
+  <si>
+    <t>1216916670897032</t>
+  </si>
+  <si>
+    <t>1216916670897033</t>
+  </si>
+  <si>
+    <t>1216916670897034</t>
+  </si>
+  <si>
+    <t>1216916670897035</t>
+  </si>
+  <si>
+    <t>1216916670897036</t>
+  </si>
+  <si>
+    <t>1216916670897037</t>
+  </si>
+  <si>
+    <t>1216916670897038</t>
+  </si>
+  <si>
+    <t>1216916670897039</t>
+  </si>
+  <si>
+    <t>1216916670897040</t>
+  </si>
+  <si>
+    <t>1216916670897041</t>
+  </si>
+  <si>
+    <t>1216916670897042</t>
+  </si>
+  <si>
+    <t>1216916670897043</t>
+  </si>
+  <si>
+    <t>1216950957319507</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Armado de rodete  OT 4382 - OT 4383  </t>
+  </si>
+  <si>
+    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Montaje:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
+  </si>
+  <si>
     <t>Media</t>
-  </si>
-  <si>
-    <t>1216950807852788</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950807852806</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950957312170</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
-  </si>
-  <si>
-    <t>1216950957319489</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,Revestimiento OT 4382 - OT 4383 </t>
-  </si>
-  <si>
-    <t>1216916670897023</t>
-  </si>
-  <si>
-    <t>1216916670897024</t>
-  </si>
-  <si>
-    <t>1216916670897025</t>
-  </si>
-  <si>
-    <t>1216916670897026</t>
-  </si>
-  <si>
-    <t>1216916670897027</t>
-  </si>
-  <si>
-    <t>1216916670897028</t>
-  </si>
-  <si>
-    <t>1216916670897029</t>
-  </si>
-  <si>
-    <t>1216916670897030</t>
-  </si>
-  <si>
-    <t>1216916670897031</t>
-  </si>
-  <si>
-    <t>1216916670897032</t>
-  </si>
-  <si>
-    <t>1216916670897033</t>
-  </si>
-  <si>
-    <t>1216916670897034</t>
-  </si>
-  <si>
-    <t>1216916670897035</t>
-  </si>
-  <si>
-    <t>1216916670897036</t>
-  </si>
-  <si>
-    <t>1216916670897037</t>
-  </si>
-  <si>
-    <t>1216916670897038</t>
-  </si>
-  <si>
-    <t>1216916670897039</t>
-  </si>
-  <si>
-    <t>1216916670897040</t>
-  </si>
-  <si>
-    <t>1216916670897041</t>
-  </si>
-  <si>
-    <t>1216916670897042</t>
-  </si>
-  <si>
-    <t>1216916670897043</t>
-  </si>
-  <si>
-    <t>1216950957319507</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Armado de rodete  OT 4382 - OT 4383  </t>
-  </si>
-  <si>
-    <t>ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Montaje:,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot 4383  - ZVN 1-9-63/2 + TOB + REJ + TIPO A,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A ,ot  4382 -ZVN 1-9-86/2 + TOB+ REJ + TIPO A </t>
   </si>
   <si>
     <t>1216950957327784</t>
@@ -10031,7 +10031,7 @@
       </c>
       <c r="C137" s="10"/>
       <c r="D137" s="9">
-        <v>46274.16181846065</v>
+        <v>46282.16090332176</v>
       </c>
       <c r="E137" s="10" t="s">
         <v>300</v>
@@ -10075,8 +10075,8 @@
       <c r="R137" s="9">
         <v>46275</v>
       </c>
-      <c r="S137" s="12" t="s">
-        <v>302</v>
+      <c r="S137" s="11" t="s">
+        <v>56</v>
       </c>
       <c r="T137" s="10">
         <v>0</v>
@@ -10087,7 +10087,7 @@
     </row>
     <row r="138" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A138" s="4" t="s">
-        <v>303</v>
+        <v>302</v>
       </c>
       <c r="B138" s="5">
         <v>46231.56056978009</v>
@@ -10130,7 +10130,7 @@
         <v>134</v>
       </c>
       <c r="P138" s="6" t="s">
-        <v>304</v>
+        <v>303</v>
       </c>
       <c r="Q138" s="6"/>
       <c r="R138" s="6"/>
@@ -10140,7 +10140,7 @@
     </row>
     <row r="139" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A139" s="8" t="s">
-        <v>305</v>
+        <v>304</v>
       </c>
       <c r="B139" s="9">
         <v>46231.56057377315</v>
@@ -10183,7 +10183,7 @@
         <v>134</v>
       </c>
       <c r="P139" s="10" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q139" s="10"/>
       <c r="R139" s="10"/>
@@ -10193,7 +10193,7 @@
     </row>
     <row r="140" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A140" s="4" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="B140" s="5">
         <v>46231.56057756944</v>
@@ -10236,7 +10236,7 @@
         <v>134</v>
       </c>
       <c r="P140" s="6" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="Q140" s="6"/>
       <c r="R140" s="6"/>
@@ -10246,7 +10246,7 @@
     </row>
     <row r="141" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A141" s="8" t="s">
-        <v>309</v>
+        <v>308</v>
       </c>
       <c r="B141" s="9">
         <v>46231.56058153935</v>
@@ -10289,7 +10289,7 @@
         <v>134</v>
       </c>
       <c r="P141" s="10" t="s">
-        <v>310</v>
+        <v>309</v>
       </c>
       <c r="Q141" s="10"/>
       <c r="R141" s="10"/>
@@ -10299,7 +10299,7 @@
     </row>
     <row r="142" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A142" s="4" t="s">
-        <v>311</v>
+        <v>310</v>
       </c>
       <c r="B142" s="5">
         <v>46231.579119814814</v>
@@ -10352,7 +10352,7 @@
     </row>
     <row r="143" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A143" s="8" t="s">
-        <v>312</v>
+        <v>311</v>
       </c>
       <c r="B143" s="9">
         <v>46231.57913229166</v>
@@ -10405,7 +10405,7 @@
     </row>
     <row r="144" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A144" s="4" t="s">
-        <v>313</v>
+        <v>312</v>
       </c>
       <c r="B144" s="5">
         <v>46231.579153576386</v>
@@ -10458,7 +10458,7 @@
     </row>
     <row r="145" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A145" s="8" t="s">
-        <v>314</v>
+        <v>313</v>
       </c>
       <c r="B145" s="9">
         <v>46231.57915875</v>
@@ -10511,7 +10511,7 @@
     </row>
     <row r="146" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A146" s="4" t="s">
-        <v>315</v>
+        <v>314</v>
       </c>
       <c r="B146" s="5">
         <v>46231.5791637963</v>
@@ -10564,7 +10564,7 @@
     </row>
     <row r="147" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A147" s="8" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="B147" s="9">
         <v>46231.57917025463</v>
@@ -10617,7 +10617,7 @@
     </row>
     <row r="148" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A148" s="4" t="s">
-        <v>317</v>
+        <v>316</v>
       </c>
       <c r="B148" s="5">
         <v>46231.579175439816</v>
@@ -10670,7 +10670,7 @@
     </row>
     <row r="149" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A149" s="8" t="s">
-        <v>318</v>
+        <v>317</v>
       </c>
       <c r="B149" s="9">
         <v>46231.579188055555</v>
@@ -10723,7 +10723,7 @@
     </row>
     <row r="150" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A150" s="4" t="s">
-        <v>319</v>
+        <v>318</v>
       </c>
       <c r="B150" s="5">
         <v>46231.57919295139</v>
@@ -10776,7 +10776,7 @@
     </row>
     <row r="151" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A151" s="8" t="s">
-        <v>320</v>
+        <v>319</v>
       </c>
       <c r="B151" s="9">
         <v>46231.579199733795</v>
@@ -10829,7 +10829,7 @@
     </row>
     <row r="152" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A152" s="4" t="s">
-        <v>321</v>
+        <v>320</v>
       </c>
       <c r="B152" s="5">
         <v>46231.579205497685</v>
@@ -10882,7 +10882,7 @@
     </row>
     <row r="153" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A153" s="8" t="s">
-        <v>322</v>
+        <v>321</v>
       </c>
       <c r="B153" s="9">
         <v>46231.57932185185</v>
@@ -10935,7 +10935,7 @@
     </row>
     <row r="154" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A154" s="4" t="s">
-        <v>323</v>
+        <v>322</v>
       </c>
       <c r="B154" s="5">
         <v>46231.57933148148</v>
@@ -10988,7 +10988,7 @@
     </row>
     <row r="155" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A155" s="8" t="s">
-        <v>324</v>
+        <v>323</v>
       </c>
       <c r="B155" s="9">
         <v>46231.579340578704</v>
@@ -11041,7 +11041,7 @@
     </row>
     <row r="156" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A156" s="4" t="s">
-        <v>325</v>
+        <v>324</v>
       </c>
       <c r="B156" s="5">
         <v>46231.57934844907</v>
@@ -11094,7 +11094,7 @@
     </row>
     <row r="157" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A157" s="8" t="s">
-        <v>326</v>
+        <v>325</v>
       </c>
       <c r="B157" s="9">
         <v>46231.57935601852</v>
@@ -11147,7 +11147,7 @@
     </row>
     <row r="158" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A158" s="4" t="s">
-        <v>327</v>
+        <v>326</v>
       </c>
       <c r="B158" s="5">
         <v>46231.579362268516</v>
@@ -11200,7 +11200,7 @@
     </row>
     <row r="159" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A159" s="8" t="s">
-        <v>328</v>
+        <v>327</v>
       </c>
       <c r="B159" s="9">
         <v>46231.57937175926</v>
@@ -11253,7 +11253,7 @@
     </row>
     <row r="160" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A160" s="4" t="s">
-        <v>329</v>
+        <v>328</v>
       </c>
       <c r="B160" s="5">
         <v>46231.57937903935</v>
@@ -11306,7 +11306,7 @@
     </row>
     <row r="161" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A161" s="8" t="s">
-        <v>330</v>
+        <v>329</v>
       </c>
       <c r="B161" s="9">
         <v>46231.57938550926</v>
@@ -11359,7 +11359,7 @@
     </row>
     <row r="162" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A162" s="4" t="s">
-        <v>331</v>
+        <v>330</v>
       </c>
       <c r="B162" s="5">
         <v>46231.579394479166</v>
@@ -11412,7 +11412,7 @@
     </row>
     <row r="163" spans="1:21" x14ac:dyDescent="0.25">
       <c r="A163" s="8" t="s">
-        <v>332</v>
+        <v>331</v>
       </c>
       <c r="B163" s="9">
         <v>46231.560585</v>
@@ -11422,7 +11422,7 @@
         <v>46279.14898133102</v>
       </c>
       <c r="E163" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="F163" s="10" t="s">
         <v>26</v>
@@ -11452,10 +11452,10 @@
         <v>297</v>
       </c>
       <c r="O163" s="10" t="s">
+        <v>333</v>
+      </c>
+      <c r="P163" s="10" t="s">
         <v>334</v>
-      </c>
-      <c r="P163" s="10" t="s">
-        <v>335</v>
       </c>
       <c r="Q163" s="9">
         <v>46286</v>
@@ -11464,7 +11464,7 @@
         <v>46286</v>
       </c>
       <c r="S163" s="12" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="T163" s="10">
         <v>0</v>
@@ -11512,13 +11512,13 @@
         <v>26</v>
       </c>
       <c r="N164" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O164" s="6" t="s">
         <v>337</v>
       </c>
       <c r="P164" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q164" s="6"/>
       <c r="R164" s="6"/>
@@ -11565,13 +11565,13 @@
         <v>26</v>
       </c>
       <c r="N165" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O165" s="10" t="s">
         <v>339</v>
       </c>
       <c r="P165" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q165" s="10"/>
       <c r="R165" s="10"/>
@@ -11618,13 +11618,13 @@
         <v>26</v>
       </c>
       <c r="N166" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O166" s="6" t="s">
         <v>337</v>
       </c>
       <c r="P166" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q166" s="6"/>
       <c r="R166" s="6"/>
@@ -11671,7 +11671,7 @@
         <v>26</v>
       </c>
       <c r="N167" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O167" s="10" t="s">
         <v>342</v>
@@ -11724,13 +11724,13 @@
         <v>26</v>
       </c>
       <c r="N168" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O168" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P168" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q168" s="6"/>
       <c r="R168" s="6"/>
@@ -11777,13 +11777,13 @@
         <v>26</v>
       </c>
       <c r="N169" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O169" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P169" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q169" s="10"/>
       <c r="R169" s="10"/>
@@ -11830,13 +11830,13 @@
         <v>26</v>
       </c>
       <c r="N170" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O170" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P170" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q170" s="6"/>
       <c r="R170" s="6"/>
@@ -11883,13 +11883,13 @@
         <v>26</v>
       </c>
       <c r="N171" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O171" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P171" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q171" s="10"/>
       <c r="R171" s="10"/>
@@ -11936,13 +11936,13 @@
         <v>26</v>
       </c>
       <c r="N172" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O172" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P172" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q172" s="6"/>
       <c r="R172" s="6"/>
@@ -11989,13 +11989,13 @@
         <v>26</v>
       </c>
       <c r="N173" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O173" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P173" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q173" s="10"/>
       <c r="R173" s="10"/>
@@ -12042,13 +12042,13 @@
         <v>26</v>
       </c>
       <c r="N174" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O174" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P174" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q174" s="6"/>
       <c r="R174" s="6"/>
@@ -12095,13 +12095,13 @@
         <v>26</v>
       </c>
       <c r="N175" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O175" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P175" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q175" s="10"/>
       <c r="R175" s="10"/>
@@ -12148,13 +12148,13 @@
         <v>26</v>
       </c>
       <c r="N176" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O176" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P176" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q176" s="6"/>
       <c r="R176" s="6"/>
@@ -12201,13 +12201,13 @@
         <v>26</v>
       </c>
       <c r="N177" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O177" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P177" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q177" s="10"/>
       <c r="R177" s="10"/>
@@ -12254,13 +12254,13 @@
         <v>26</v>
       </c>
       <c r="N178" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O178" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P178" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q178" s="6"/>
       <c r="R178" s="6"/>
@@ -12307,13 +12307,13 @@
         <v>26</v>
       </c>
       <c r="N179" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O179" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P179" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q179" s="10"/>
       <c r="R179" s="10"/>
@@ -12360,13 +12360,13 @@
         <v>26</v>
       </c>
       <c r="N180" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O180" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P180" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q180" s="6"/>
       <c r="R180" s="6"/>
@@ -12413,13 +12413,13 @@
         <v>26</v>
       </c>
       <c r="N181" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O181" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P181" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q181" s="10"/>
       <c r="R181" s="10"/>
@@ -12466,13 +12466,13 @@
         <v>26</v>
       </c>
       <c r="N182" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O182" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P182" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q182" s="6"/>
       <c r="R182" s="6"/>
@@ -12519,13 +12519,13 @@
         <v>26</v>
       </c>
       <c r="N183" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O183" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P183" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q183" s="10"/>
       <c r="R183" s="10"/>
@@ -12572,13 +12572,13 @@
         <v>26</v>
       </c>
       <c r="N184" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O184" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P184" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q184" s="6"/>
       <c r="R184" s="6"/>
@@ -12625,13 +12625,13 @@
         <v>26</v>
       </c>
       <c r="N185" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O185" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P185" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q185" s="10"/>
       <c r="R185" s="10"/>
@@ -12678,13 +12678,13 @@
         <v>26</v>
       </c>
       <c r="N186" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O186" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P186" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q186" s="6"/>
       <c r="R186" s="6"/>
@@ -12731,13 +12731,13 @@
         <v>26</v>
       </c>
       <c r="N187" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O187" s="10" t="s">
         <v>345</v>
       </c>
       <c r="P187" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q187" s="10"/>
       <c r="R187" s="10"/>
@@ -12784,13 +12784,13 @@
         <v>26</v>
       </c>
       <c r="N188" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="O188" s="6" t="s">
         <v>345</v>
       </c>
       <c r="P188" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="Q188" s="6"/>
       <c r="R188" s="6"/>
@@ -12852,7 +12852,7 @@
         <v>46287</v>
       </c>
       <c r="S189" s="12" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="T189" s="10">
         <v>0</v>
@@ -14240,7 +14240,7 @@
         <v>46288</v>
       </c>
       <c r="S215" s="12" t="s">
-        <v>302</v>
+        <v>335</v>
       </c>
       <c r="T215" s="10">
         <v>0</v>
@@ -14503,7 +14503,7 @@
         <v>398</v>
       </c>
       <c r="O220" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P220" s="6" t="s">
         <v>398</v>
@@ -14556,7 +14556,7 @@
         <v>398</v>
       </c>
       <c r="O221" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P221" s="10" t="s">
         <v>398</v>
@@ -14662,7 +14662,7 @@
         <v>398</v>
       </c>
       <c r="O223" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P223" s="10" t="s">
         <v>398</v>
@@ -14715,7 +14715,7 @@
         <v>398</v>
       </c>
       <c r="O224" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P224" s="6" t="s">
         <v>398</v>
@@ -14768,7 +14768,7 @@
         <v>398</v>
       </c>
       <c r="O225" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P225" s="10" t="s">
         <v>398</v>
@@ -14821,7 +14821,7 @@
         <v>398</v>
       </c>
       <c r="O226" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P226" s="6" t="s">
         <v>398</v>
@@ -14874,7 +14874,7 @@
         <v>398</v>
       </c>
       <c r="O227" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P227" s="10" t="s">
         <v>398</v>
@@ -14927,7 +14927,7 @@
         <v>398</v>
       </c>
       <c r="O228" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P228" s="6" t="s">
         <v>398</v>
@@ -14980,7 +14980,7 @@
         <v>398</v>
       </c>
       <c r="O229" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P229" s="10" t="s">
         <v>398</v>
@@ -15033,7 +15033,7 @@
         <v>398</v>
       </c>
       <c r="O230" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P230" s="6" t="s">
         <v>398</v>
@@ -15086,7 +15086,7 @@
         <v>398</v>
       </c>
       <c r="O231" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P231" s="10" t="s">
         <v>398</v>
@@ -15139,7 +15139,7 @@
         <v>398</v>
       </c>
       <c r="O232" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P232" s="6" t="s">
         <v>398</v>
@@ -15192,7 +15192,7 @@
         <v>398</v>
       </c>
       <c r="O233" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P233" s="10" t="s">
         <v>398</v>
@@ -15245,7 +15245,7 @@
         <v>398</v>
       </c>
       <c r="O234" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P234" s="6" t="s">
         <v>398</v>
@@ -15298,7 +15298,7 @@
         <v>398</v>
       </c>
       <c r="O235" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P235" s="10" t="s">
         <v>398</v>
@@ -15351,7 +15351,7 @@
         <v>398</v>
       </c>
       <c r="O236" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P236" s="6" t="s">
         <v>398</v>
@@ -15404,7 +15404,7 @@
         <v>398</v>
       </c>
       <c r="O237" s="10" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P237" s="10" t="s">
         <v>398</v>
@@ -15457,7 +15457,7 @@
         <v>398</v>
       </c>
       <c r="O238" s="6" t="s">
-        <v>333</v>
+        <v>332</v>
       </c>
       <c r="P238" s="6" t="s">
         <v>398</v>
@@ -19809,7 +19809,7 @@
         <v>518</v>
       </c>
       <c r="O320" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P320" s="6" t="s">
         <v>524</v>
@@ -23973,7 +23973,7 @@
         <v>518</v>
       </c>
       <c r="O398" s="6" t="s">
-        <v>334</v>
+        <v>333</v>
       </c>
       <c r="P398" s="6" t="s">
         <v>619</v>
